--- a/grupos/5ALCV - Estadisticos 20211.xlsx
+++ b/grupos/5ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -191,12 +191,12 @@
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -218,226 +218,226 @@
     <t>ALONSO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>NOLASCO</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>MELISSA VIANNEY</t>
+  </si>
+  <si>
+    <t>CONCEPCION</t>
+  </si>
+  <si>
+    <t>KARLA MICHEL</t>
+  </si>
+  <si>
+    <t>YADIRA</t>
+  </si>
+  <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>NOLASCO</t>
+    <t>LAZARO</t>
+  </si>
+  <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TORRES</t>
   </si>
   <si>
     <t>SALGADO</t>
   </si>
   <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>MELISSA VIANNEY</t>
+    <t>VARGAS</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>BITHIA MARIAN</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
+    <t>BRENDA JANET</t>
+  </si>
+  <si>
+    <t>ADOLFO ANTONIO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>AZAEL</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
   </si>
   <si>
     <t>ROBERTO JESUS</t>
-  </si>
-  <si>
-    <t>CONCEPCION</t>
-  </si>
-  <si>
-    <t>KARLA MICHEL</t>
-  </si>
-  <si>
-    <t>YADIRA</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DEGANTE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>BITHIA MARIAN</t>
-  </si>
-  <si>
-    <t>IRIDIA</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>ADOLFO ANTONIO</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>SHARITH</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>AZAEL</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
   </si>
   <si>
     <t>ANGEL ALEXIS</t>
@@ -989,13 +989,13 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -1004,7 +1004,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1040,7 +1040,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1066,13 +1066,13 @@
         <v>8</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -1081,7 +1081,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>8</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1117,7 +1117,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1143,13 +1143,13 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -1158,7 +1158,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1179,7 +1179,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>9</v>
@@ -1235,7 +1235,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1297,13 +1297,13 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1333,7 +1333,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1348,7 +1348,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1377,7 +1377,7 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>-1</v>
@@ -1389,7 +1389,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1413,7 +1413,7 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>9</v>
@@ -1425,7 +1425,7 @@
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1451,13 +1451,13 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -1466,7 +1466,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1502,7 +1502,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1528,13 +1528,13 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -1543,7 +1543,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1564,13 +1564,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>5</v>
@@ -1596,7 +1596,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1608,7 +1608,7 @@
         <v>5</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1634,10 +1634,10 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J13">
         <v>-1</v>
@@ -1649,7 +1649,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1711,13 +1711,13 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1726,7 +1726,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1747,13 +1747,13 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
         <v>7</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -1788,13 +1788,13 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1803,7 +1803,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>8</v>
@@ -1865,13 +1865,13 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1880,7 +1880,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1927,10 +1927,10 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E17">
         <v>5</v>
@@ -1945,10 +1945,10 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1957,7 +1957,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1981,10 +1981,10 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W17">
         <v>5</v>
@@ -2019,13 +2019,13 @@
         <v>9</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -2034,7 +2034,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2070,7 +2070,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2099,7 +2099,7 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J19">
         <v>-1</v>
@@ -2111,7 +2111,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2135,7 +2135,7 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2176,10 +2176,10 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2188,7 +2188,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2215,7 +2215,7 @@
         <v>7</v>
       </c>
       <c r="V20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2250,13 +2250,13 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K21">
         <v>-1</v>
@@ -2265,7 +2265,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2318,7 +2318,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2330,7 +2330,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2356,10 +2356,10 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>-1</v>
@@ -2371,7 +2371,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2395,7 +2395,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -2433,13 +2433,13 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -2448,7 +2448,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2475,7 +2475,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2484,7 +2484,7 @@
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2510,10 +2510,10 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1</v>
@@ -2525,7 +2525,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2549,7 +2549,7 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V25">
         <v>8</v>
@@ -2587,10 +2587,10 @@
         <v>9</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J26">
         <v>-1</v>
@@ -2602,7 +2602,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2623,7 +2623,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>8</v>
@@ -2664,13 +2664,13 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -2679,7 +2679,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2703,10 +2703,10 @@
         <v>8</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>6</v>
@@ -2715,7 +2715,7 @@
         <v>8</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2741,13 +2741,13 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -2756,7 +2756,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2792,7 +2792,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2818,13 +2818,13 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -2833,7 +2833,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2854,13 +2854,13 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>6</v>
@@ -2895,13 +2895,13 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -2910,7 +2910,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2937,7 +2937,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -2972,13 +2972,13 @@
         <v>8</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -2987,7 +2987,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3011,7 +3011,7 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3023,7 +3023,7 @@
         <v>9</v>
       </c>
       <c r="Y31">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3049,13 +3049,13 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K32">
         <v>-1</v>
@@ -3064,7 +3064,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3091,7 +3091,7 @@
         <v>9</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3100,7 +3100,7 @@
         <v>10</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3123,7 +3123,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3141,7 +3141,7 @@
         <v>-1</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3167,13 +3167,13 @@
         <v>9</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K34">
         <v>-1</v>
@@ -3182,7 +3182,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3206,10 +3206,10 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3218,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3244,13 +3244,13 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -3259,7 +3259,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3321,13 +3321,13 @@
         <v>10</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -3336,7 +3336,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3360,10 +3360,10 @@
         <v>9</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W36">
         <v>6</v>
@@ -3372,7 +3372,7 @@
         <v>10</v>
       </c>
       <c r="Y36">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3398,13 +3398,13 @@
         <v>10</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
@@ -3413,7 +3413,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3546,19 +3546,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>76.47</v>
+        <v>79.41</v>
       </c>
       <c r="G3">
-        <v>23.53</v>
+        <v>20.59</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3569,66 +3569,66 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>78.13</v>
+        <v>83.87</v>
       </c>
       <c r="G4">
-        <v>12.5</v>
+        <v>6.45</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <v>9.380000000000001</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>87.09999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="H5">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J5">
-        <v>12.9</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3702,7 +3702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3737,16 +3737,16 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3757,16 +3757,16 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3777,10 +3777,10 @@
         <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -3791,19 +3791,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920420</v>
+        <v>19330051920284</v>
       </c>
       <c r="B5" t="s">
         <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
         <v>57</v>
@@ -3811,82 +3811,42 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920420</v>
+        <v>19330051920289</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
         <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>19330051920284</v>
+        <v>18330051920346</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>19330051920289</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>18330051920346</v>
-      </c>
-      <c r="B9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -3928,10 +3888,10 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -3939,33 +3899,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920420</v>
+        <v>19330051920284</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920284</v>
+        <v>19330051920289</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -3973,16 +3933,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>19330051920289</v>
+        <v>18330051920346</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -3990,30 +3950,30 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>18330051920346</v>
+        <v>19330051920270</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>127</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920270</v>
+        <v>19330051920272</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="D7" t="s">
         <v>128</v>
@@ -4024,13 +3984,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920272</v>
+        <v>19330051920269</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
         <v>129</v>
@@ -4041,13 +4001,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920269</v>
+        <v>19330051920273</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
         <v>130</v>
@@ -4058,13 +4018,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920273</v>
+        <v>19330051920268</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -4075,13 +4035,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920268</v>
+        <v>19330051920274</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
         <v>132</v>
@@ -4092,13 +4052,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>19330051920274</v>
+        <v>18330051920242</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -4109,13 +4069,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>18330051920242</v>
+        <v>18330051920319</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
         <v>134</v>
@@ -4126,13 +4086,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>18330051920319</v>
+        <v>18330051920321</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4143,13 +4103,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>18330051920321</v>
+        <v>19330051920278</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4160,13 +4120,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920278</v>
+        <v>19330051920449</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4177,13 +4137,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920449</v>
+        <v>19330051920279</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4194,13 +4154,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920279</v>
+        <v>19330051920420</v>
       </c>
       <c r="B18" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4214,10 +4174,10 @@
         <v>19330051920447</v>
       </c>
       <c r="B19" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4231,10 +4191,10 @@
         <v>19330051920286</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C20" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4248,10 +4208,10 @@
         <v>18330051920336</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4265,10 +4225,10 @@
         <v>19330051920287</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4282,10 +4242,10 @@
         <v>19330051920343</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4299,10 +4259,10 @@
         <v>19330051920292</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4316,10 +4276,10 @@
         <v>19330051920293</v>
       </c>
       <c r="B25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4333,10 +4293,10 @@
         <v>19330051920294</v>
       </c>
       <c r="B26" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4350,10 +4310,10 @@
         <v>19330051920296</v>
       </c>
       <c r="B27" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C27" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4367,10 +4327,10 @@
         <v>19330051920295</v>
       </c>
       <c r="B28" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C28" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4384,10 +4344,10 @@
         <v>19330051920297</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D29" t="s">
         <v>150</v>
@@ -4401,10 +4361,10 @@
         <v>19330051920298</v>
       </c>
       <c r="B30" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
         <v>148</v>
@@ -4418,10 +4378,10 @@
         <v>19330051920299</v>
       </c>
       <c r="B31" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C31" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -4435,10 +4395,10 @@
         <v>19330051920301</v>
       </c>
       <c r="B32" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -4452,10 +4412,10 @@
         <v>19330051920443</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4469,10 +4429,10 @@
         <v>19330051920300</v>
       </c>
       <c r="B34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C34" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4486,10 +4446,10 @@
         <v>19330051920305</v>
       </c>
       <c r="B35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4505,7 +4465,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4537,39 +4497,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>18330051920242</v>
+        <v>19330051920284</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>57</v>
       </c>
       <c r="G2">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>18330051920242</v>
+        <v>19330051920284</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4583,39 +4543,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920278</v>
+        <v>19330051920289</v>
       </c>
       <c r="B4" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920278</v>
+        <v>19330051920289</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4629,68 +4589,68 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920284</v>
+        <v>18330051920346</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
         <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920284</v>
+        <v>18330051920346</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
         <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920286</v>
+        <v>19330051920269</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C8" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="D8" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4698,22 +4658,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920286</v>
+        <v>19330051920273</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="D9" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4721,22 +4681,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>18330051920346</v>
+        <v>19330051920268</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4744,45 +4704,45 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920346</v>
+        <v>18330051920242</v>
       </c>
       <c r="B11" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>108</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920269</v>
+        <v>18330051920319</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4790,22 +4750,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920273</v>
+        <v>18330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C13" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4813,22 +4773,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920268</v>
+        <v>19330051920278</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4836,22 +4796,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>18330051920319</v>
+        <v>19330051920449</v>
       </c>
       <c r="B15" t="s">
         <v>87</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4859,22 +4819,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920321</v>
+        <v>18330051920336</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4882,16 +4842,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920449</v>
+        <v>19330051920343</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -4905,22 +4865,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330051920336</v>
+        <v>19330051920292</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C18" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -4928,16 +4888,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920343</v>
+        <v>19330051920293</v>
       </c>
       <c r="B19" t="s">
         <v>95</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>119</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4951,16 +4911,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920292</v>
+        <v>19330051920298</v>
       </c>
       <c r="B20" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C20" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4974,16 +4934,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920293</v>
+        <v>19330051920299</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4997,16 +4957,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920298</v>
+        <v>19330051920443</v>
       </c>
       <c r="B22" t="s">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="C22" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D22" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -5015,75 +4975,6 @@
         <v>55</v>
       </c>
       <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920299</v>
-      </c>
-      <c r="B23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" t="s">
-        <v>124</v>
-      </c>
-      <c r="D23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920301</v>
-      </c>
-      <c r="B24" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" t="s">
-        <v>125</v>
-      </c>
-      <c r="D24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>57</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920443</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>126</v>
-      </c>
-      <c r="D25" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20211.xlsx
+++ b/grupos/5ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -998,7 +998,7 @@
         <v>7</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
         <v>-1</v>
@@ -1075,7 +1075,7 @@
         <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L5">
         <v>-1</v>
@@ -1152,7 +1152,7 @@
         <v>10</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L6">
         <v>-1</v>
@@ -1211,7 +1211,7 @@
         <v>-1</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -1229,7 +1229,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>-1</v>
@@ -1265,7 +1265,7 @@
         <v>-1</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="X7">
         <v>5</v>
@@ -1306,7 +1306,7 @@
         <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
         <v>-1</v>
@@ -1383,7 +1383,7 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L9">
         <v>-1</v>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1460,7 +1460,7 @@
         <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
         <v>-1</v>
@@ -1537,7 +1537,7 @@
         <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L11">
         <v>-1</v>
@@ -1643,7 +1643,7 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1720,7 +1720,7 @@
         <v>4</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L14">
         <v>-1</v>
@@ -1797,7 +1797,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L15">
         <v>-1</v>
@@ -1874,7 +1874,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>-1</v>
@@ -1910,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>9</v>
@@ -1951,7 +1951,7 @@
         <v>5</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
         <v>-1</v>
@@ -2064,7 +2064,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2105,7 +2105,7 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L19">
         <v>-1</v>
@@ -2182,7 +2182,7 @@
         <v>4</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
         <v>-1</v>
@@ -2259,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L21">
         <v>-1</v>
@@ -2295,7 +2295,7 @@
         <v>10</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2365,7 +2365,7 @@
         <v>-1</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L23">
         <v>-1</v>
@@ -2442,7 +2442,7 @@
         <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>-1</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L25">
         <v>-1</v>
@@ -2596,7 +2596,7 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
         <v>-1</v>
@@ -2673,7 +2673,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L27">
         <v>-1</v>
@@ -2709,7 +2709,7 @@
         <v>9</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X27">
         <v>8</v>
@@ -2750,7 +2750,7 @@
         <v>9</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>-1</v>
@@ -2786,7 +2786,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
         <v>-1</v>
@@ -2863,7 +2863,7 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>8</v>
@@ -2904,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L30">
         <v>-1</v>
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2981,7 +2981,7 @@
         <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L31">
         <v>-1</v>
@@ -3058,7 +3058,7 @@
         <v>7</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
         <v>-1</v>
@@ -3176,7 +3176,7 @@
         <v>4</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
         <v>-1</v>
@@ -3253,7 +3253,7 @@
         <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>-1</v>
@@ -3289,7 +3289,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>9</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L36">
         <v>-1</v>
@@ -3366,7 +3366,7 @@
         <v>9</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X36">
         <v>10</v>
@@ -3407,7 +3407,7 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
         <v>-1</v>
@@ -3514,25 +3514,25 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2">
-        <v>48.39</v>
+        <v>38.71</v>
       </c>
       <c r="G2">
-        <v>48.39</v>
+        <v>61.29</v>
       </c>
       <c r="H2">
         <v>6.2</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>3.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3702,7 +3702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3771,36 +3771,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>19330051920271</v>
+        <v>19330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>19330051920284</v>
+        <v>19330051920289</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -3811,41 +3811,21 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>19330051920289</v>
+        <v>18330051920346</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>18330051920346</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3894,7 +3874,7 @@
         <v>73</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4465,7 +4445,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4497,39 +4477,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920284</v>
+        <v>19330051920273</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920284</v>
+        <v>19330051920273</v>
       </c>
       <c r="B3" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>105</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>130</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4543,16 +4523,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920289</v>
+        <v>19330051920284</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -4566,16 +4546,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920289</v>
+        <v>19330051920284</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4589,68 +4569,68 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>18330051920346</v>
+        <v>19330051920289</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>18330051920346</v>
+        <v>19330051920289</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920269</v>
+        <v>18330051920346</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4658,45 +4638,45 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920273</v>
+        <v>18330051920346</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>130</v>
+        <v>76</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920268</v>
+        <v>19330051920269</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -4704,22 +4684,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>18330051920242</v>
+        <v>19330051920268</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4727,22 +4707,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920319</v>
+        <v>18330051920242</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4750,22 +4730,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>18330051920321</v>
+        <v>18330051920319</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4773,16 +4753,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920278</v>
+        <v>18330051920321</v>
       </c>
       <c r="B14" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4796,16 +4776,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920449</v>
+        <v>19330051920278</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4819,22 +4799,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920336</v>
+        <v>19330051920449</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4842,22 +4822,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920343</v>
+        <v>18330051920336</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -4865,16 +4845,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>19330051920292</v>
+        <v>19330051920343</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -4888,16 +4868,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>19330051920293</v>
+        <v>19330051920292</v>
       </c>
       <c r="B19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="D19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -4911,16 +4891,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920298</v>
+        <v>19330051920293</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -4934,16 +4914,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920299</v>
+        <v>19330051920295</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -4957,16 +4937,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>19330051920443</v>
+        <v>19330051920298</v>
       </c>
       <c r="B22" t="s">
-        <v>68</v>
+        <v>99</v>
       </c>
       <c r="C22" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -4975,6 +4955,75 @@
         <v>55</v>
       </c>
       <c r="G22">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920299</v>
+      </c>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>19330051920301</v>
+      </c>
+      <c r="B24" t="s">
+        <v>101</v>
+      </c>
+      <c r="C24" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
+      <c r="G24">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>19330051920443</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" t="s">
+        <v>153</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G25">
         <v>5</v>
       </c>
     </row>

--- a/grupos/5ALCV - Estadisticos 20211.xlsx
+++ b/grupos/5ALCV - Estadisticos 20211.xlsx
@@ -1001,7 +1001,7 @@
         <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
         <v>9</v>
@@ -1037,7 +1037,7 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1078,7 +1078,7 @@
         <v>5</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>6</v>
@@ -1114,7 +1114,7 @@
         <v>5</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1155,7 +1155,7 @@
         <v>8</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
         <v>10</v>
@@ -1191,7 +1191,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y6">
         <v>10</v>
@@ -1232,7 +1232,7 @@
         <v>5</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M7">
         <v>6</v>
@@ -1309,7 +1309,7 @@
         <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
         <v>10</v>
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1386,7 +1386,7 @@
         <v>5</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1463,7 +1463,7 @@
         <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
         <v>9</v>
@@ -1499,7 +1499,7 @@
         <v>10</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1540,7 +1540,7 @@
         <v>5</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1576,7 +1576,7 @@
         <v>5</v>
       </c>
       <c r="X11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1646,7 +1646,7 @@
         <v>5</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M13">
         <v>8</v>
@@ -1723,7 +1723,7 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>8</v>
@@ -1759,7 +1759,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1800,7 +1800,7 @@
         <v>6</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>9</v>
@@ -1836,7 +1836,7 @@
         <v>5</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>10</v>
@@ -1877,7 +1877,7 @@
         <v>7</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>10</v>
@@ -1913,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1954,7 +1954,7 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>6</v>
@@ -2031,7 +2031,7 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
         <v>10</v>
@@ -2067,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
         <v>10</v>
@@ -2108,7 +2108,7 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
         <v>7</v>
@@ -2185,7 +2185,7 @@
         <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>6</v>
@@ -2262,7 +2262,7 @@
         <v>10</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M21">
         <v>10</v>
@@ -2298,7 +2298,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>8</v>
@@ -2445,7 +2445,7 @@
         <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>9</v>
@@ -2522,7 +2522,7 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
         <v>9</v>
@@ -2558,7 +2558,7 @@
         <v>5</v>
       </c>
       <c r="X25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y25">
         <v>9</v>
@@ -2599,7 +2599,7 @@
         <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>8</v>
@@ -2635,7 +2635,7 @@
         <v>5</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2676,7 +2676,7 @@
         <v>7</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>9</v>
@@ -2712,7 +2712,7 @@
         <v>7</v>
       </c>
       <c r="X27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>9</v>
@@ -2753,7 +2753,7 @@
         <v>6</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>9</v>
@@ -2830,7 +2830,7 @@
         <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M29">
         <v>8</v>
@@ -2866,7 +2866,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2907,7 +2907,7 @@
         <v>5</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>9</v>
@@ -2984,7 +2984,7 @@
         <v>6</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
         <v>10</v>
@@ -3020,7 +3020,7 @@
         <v>5</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -3061,7 +3061,7 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
         <v>10</v>
@@ -3179,7 +3179,7 @@
         <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M34">
         <v>6</v>
@@ -3215,7 +3215,7 @@
         <v>5</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>8</v>
@@ -3256,7 +3256,7 @@
         <v>10</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>10</v>
@@ -3292,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="X35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y35">
         <v>10</v>
@@ -3333,7 +3333,7 @@
         <v>5</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M36">
         <v>8</v>
@@ -3410,7 +3410,7 @@
         <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>10</v>
@@ -3446,7 +3446,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3654,7 +3654,7 @@
         <v>3.23</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/5ALCV - Estadisticos 20211.xlsx
+++ b/grupos/5ALCV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="156">
   <si>
     <t>Materia</t>
   </si>
@@ -188,15 +188,15 @@
     <t>Polanco Domínguez Rosa María</t>
   </si>
   <si>
+    <t>Domínguez Burgos Marioscar</t>
+  </si>
+  <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
     <t>Flores Ovalle Victor</t>
   </si>
   <si>
-    <t>Domínguez Burgos Marioscar</t>
-  </si>
-  <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
@@ -215,268 +215,268 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>ALCANTARA</t>
+  </si>
+  <si>
+    <t>ALTAMIRANO</t>
+  </si>
+  <si>
+    <t>AJACTLE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>ALONSO</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CANALES</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DEGANTE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LAZARO</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>MANZANET</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>TZANAHUA</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>XALAMIHUA</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>NOLASCO</t>
   </si>
   <si>
+    <t>SEGURA</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DE LOS SANTOS</t>
+  </si>
+  <si>
+    <t>LINARES</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>SALGADO</t>
+  </si>
+  <si>
+    <t>VARGAS</t>
+  </si>
+  <si>
     <t>ROQUE</t>
   </si>
   <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>BERNAL</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
+  </si>
+  <si>
+    <t>FERRAL</t>
+  </si>
+  <si>
+    <t>TZOYONTLE</t>
+  </si>
+  <si>
+    <t>GUEVARA</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>BITHIA MARIAN</t>
+  </si>
+  <si>
+    <t>IRIDIA</t>
+  </si>
+  <si>
+    <t>ELISA</t>
+  </si>
+  <si>
+    <t>ESDRAS ALAN</t>
+  </si>
+  <si>
     <t>MELISSA VIANNEY</t>
   </si>
   <si>
+    <t>BRENDA JANET</t>
+  </si>
+  <si>
+    <t>ADOLFO ANTONIO</t>
+  </si>
+  <si>
+    <t>EDITH</t>
+  </si>
+  <si>
+    <t>SHARITH</t>
+  </si>
+  <si>
+    <t>JHOVANA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>AZAEL</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
+    <t>ROBERTO JESUS</t>
+  </si>
+  <si>
+    <t>ANGEL ALEXIS</t>
+  </si>
+  <si>
     <t>CONCEPCION</t>
   </si>
   <si>
+    <t>JADE EMILY</t>
+  </si>
+  <si>
+    <t>DIEGO OLLIN</t>
+  </si>
+  <si>
+    <t>ANGEL JARET</t>
+  </si>
+  <si>
     <t>KARLA MICHEL</t>
   </si>
   <si>
+    <t>ALLISSON NICOLE</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ROSA JATZIRI</t>
+  </si>
+  <si>
+    <t>JOHANA</t>
+  </si>
+  <si>
+    <t>VALERIA GUADALUPE</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>NELLY MARLENE</t>
+  </si>
+  <si>
+    <t>CECILIA ARLETH</t>
+  </si>
+  <si>
+    <t>LAISHA STEFANY</t>
+  </si>
+  <si>
     <t>YADIRA</t>
-  </si>
-  <si>
-    <t>ALCANTARA</t>
-  </si>
-  <si>
-    <t>ALTAMIRANO</t>
-  </si>
-  <si>
-    <t>AJACTLE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CANALES</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DEGANTE</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LAZARO</t>
-  </si>
-  <si>
-    <t>MANZANET</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SERRANO</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>TZANAHUA</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>XALAMIHUA</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>SEGURA</t>
-  </si>
-  <si>
-    <t>VERA</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
-  </si>
-  <si>
-    <t>LINARES</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>SALGADO</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>BERNAL</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
-    <t>FERRAL</t>
-  </si>
-  <si>
-    <t>TZOYONTLE</t>
-  </si>
-  <si>
-    <t>GUEVARA</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>BITHIA MARIAN</t>
-  </si>
-  <si>
-    <t>IRIDIA</t>
-  </si>
-  <si>
-    <t>ELISA</t>
-  </si>
-  <si>
-    <t>ESDRAS ALAN</t>
-  </si>
-  <si>
-    <t>BRENDA JANET</t>
-  </si>
-  <si>
-    <t>ADOLFO ANTONIO</t>
-  </si>
-  <si>
-    <t>EDITH</t>
-  </si>
-  <si>
-    <t>SHARITH</t>
-  </si>
-  <si>
-    <t>JHOVANA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>AZAEL</t>
-  </si>
-  <si>
-    <t>FELIPE</t>
-  </si>
-  <si>
-    <t>ROBERTO JESUS</t>
-  </si>
-  <si>
-    <t>ANGEL ALEXIS</t>
-  </si>
-  <si>
-    <t>JADE EMILY</t>
-  </si>
-  <si>
-    <t>DIEGO OLLIN</t>
-  </si>
-  <si>
-    <t>ANGEL JARET</t>
-  </si>
-  <si>
-    <t>ALLISSON NICOLE</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ROSA JATZIRI</t>
-  </si>
-  <si>
-    <t>JOHANA</t>
-  </si>
-  <si>
-    <t>VALERIA GUADALUPE</t>
-  </si>
-  <si>
-    <t>ESMERALDA</t>
-  </si>
-  <si>
-    <t>NELLY MARLENE</t>
-  </si>
-  <si>
-    <t>CECILIA ARLETH</t>
-  </si>
-  <si>
-    <t>LAISHA STEFANY</t>
   </si>
   <si>
     <t>ASHLEY ZURELY</t>
@@ -1007,28 +1007,28 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
         <v>9</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V4">
         <v>8</v>
@@ -1040,7 +1040,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1084,31 +1084,31 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T5">
         <v>8</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
         <v>5</v>
@@ -1161,22 +1161,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -1205,10 +1205,10 @@
         <v>5</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>5</v>
@@ -1220,13 +1220,13 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>5</v>
@@ -1238,37 +1238,37 @@
         <v>6</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T7">
         <v>5</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W7">
         <v>5</v>
       </c>
       <c r="X7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y7">
         <v>6</v>
@@ -1315,28 +1315,28 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>9</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1345,7 +1345,7 @@
         <v>7</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1374,13 +1374,13 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>5</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>5</v>
@@ -1392,34 +1392,34 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X9">
         <v>8</v>
@@ -1469,22 +1469,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>8</v>
@@ -1496,7 +1496,7 @@
         <v>9</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
         <v>10</v>
@@ -1546,22 +1546,22 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>8</v>
@@ -1593,16 +1593,16 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M12">
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
         <v>5</v>
@@ -1640,7 +1640,7 @@
         <v>7</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
         <v>5</v>
@@ -1652,31 +1652,31 @@
         <v>8</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>7</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>5</v>
@@ -1685,7 +1685,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1729,28 +1729,28 @@
         <v>8</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>6</v>
@@ -1806,40 +1806,40 @@
         <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>8</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>8</v>
       </c>
       <c r="W15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1883,22 +1883,22 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>8</v>
@@ -1910,10 +1910,10 @@
         <v>10</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I17">
         <v>6</v>
@@ -1960,28 +1960,28 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
         <v>5</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -2037,22 +2037,22 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>8</v>
@@ -2084,7 +2084,7 @@
         <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E19">
         <v>5</v>
@@ -2096,13 +2096,13 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I19">
         <v>5</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K19">
         <v>5</v>
@@ -2114,31 +2114,31 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>5</v>
@@ -2147,7 +2147,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2173,7 +2173,7 @@
         <v>9</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>7</v>
@@ -2191,28 +2191,28 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V20">
         <v>5</v>
@@ -2224,7 +2224,7 @@
         <v>7</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2268,22 +2268,22 @@
         <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2298,7 +2298,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>10</v>
@@ -2315,19 +2315,19 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
         <v>6</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2344,7 +2344,7 @@
         <v>5</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E23">
         <v>5</v>
@@ -2362,7 +2362,7 @@
         <v>7</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
         <v>5</v>
@@ -2374,22 +2374,22 @@
         <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2398,7 +2398,7 @@
         <v>6</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
         <v>5</v>
@@ -2407,7 +2407,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2451,40 +2451,40 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>8</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X24">
         <v>10</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2516,7 +2516,7 @@
         <v>6</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
         <v>5</v>
@@ -2528,31 +2528,31 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>8</v>
       </c>
       <c r="U25">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W25">
         <v>5</v>
@@ -2593,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>5</v>
@@ -2605,40 +2605,40 @@
         <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>8</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>5</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2682,34 +2682,34 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T27">
         <v>8</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X27">
         <v>9</v>
@@ -2759,22 +2759,22 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T28">
         <v>8</v>
@@ -2783,7 +2783,7 @@
         <v>8</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2836,22 +2836,22 @@
         <v>8</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2863,13 +2863,13 @@
         <v>8</v>
       </c>
       <c r="W29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X29">
         <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2913,22 +2913,22 @@
         <v>9</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2940,7 +2940,7 @@
         <v>10</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>10</v>
@@ -2990,34 +2990,34 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>8</v>
       </c>
       <c r="U31">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X31">
         <v>10</v>
@@ -3067,22 +3067,22 @@
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -3111,34 +3111,34 @@
         <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G33">
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
         <v>6</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3185,22 +3185,22 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3209,7 +3209,7 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3218,7 +3218,7 @@
         <v>9</v>
       </c>
       <c r="Y34">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3262,22 +3262,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3339,22 +3339,22 @@
         <v>8</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3363,7 +3363,7 @@
         <v>6</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3416,28 +3416,28 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>8</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>9</v>
@@ -3446,7 +3446,7 @@
         <v>8</v>
       </c>
       <c r="X37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y37">
         <v>10</v>
@@ -3514,19 +3514,19 @@
         <v>31</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>38.71</v>
+        <v>54.84</v>
       </c>
       <c r="G2">
-        <v>61.29</v>
+        <v>45.16</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3537,28 +3537,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
       </c>
       <c r="C3">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>27</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>79.41</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="G3">
-        <v>20.59</v>
+        <v>12.9</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3569,66 +3569,66 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>83.87</v>
+        <v>90.63</v>
       </c>
       <c r="G4">
-        <v>6.45</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>90.63</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G5">
-        <v>3.13</v>
+        <v>8.82</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3642,19 +3642,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3686,7 +3686,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3702,7 +3702,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3727,106 +3727,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>19330051920271</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>19330051920271</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>19330051920284</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>19330051920289</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>18330051920346</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -3862,81 +3762,81 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>19330051920271</v>
+        <v>19330051920270</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>19330051920284</v>
+        <v>19330051920272</v>
       </c>
       <c r="B3" t="s">
         <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>19330051920289</v>
+        <v>19330051920269</v>
       </c>
       <c r="B4" t="s">
         <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>18330051920346</v>
+        <v>19330051920273</v>
       </c>
       <c r="B5" t="s">
         <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>19330051920270</v>
+        <v>19330051920271</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
         <v>127</v>
@@ -3947,13 +3847,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>19330051920272</v>
+        <v>19330051920268</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
         <v>128</v>
@@ -3964,13 +3864,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>19330051920269</v>
+        <v>19330051920274</v>
       </c>
       <c r="B8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
         <v>129</v>
@@ -3981,13 +3881,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>19330051920273</v>
+        <v>18330051920242</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
         <v>130</v>
@@ -3998,13 +3898,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>19330051920268</v>
+        <v>18330051920319</v>
       </c>
       <c r="B10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
         <v>131</v>
@@ -4015,13 +3915,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>19330051920274</v>
+        <v>18330051920321</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
         <v>132</v>
@@ -4032,13 +3932,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>18330051920242</v>
+        <v>19330051920278</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
         <v>133</v>
@@ -4049,13 +3949,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>18330051920319</v>
+        <v>19330051920449</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D13" t="s">
         <v>134</v>
@@ -4066,13 +3966,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>18330051920321</v>
+        <v>19330051920279</v>
       </c>
       <c r="B14" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
         <v>135</v>
@@ -4083,13 +3983,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>19330051920278</v>
+        <v>19330051920420</v>
       </c>
       <c r="B15" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
         <v>136</v>
@@ -4100,13 +4000,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>19330051920449</v>
+        <v>19330051920447</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
         <v>137</v>
@@ -4117,13 +4017,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>19330051920279</v>
+        <v>19330051920284</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C17" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="D17" t="s">
         <v>138</v>
@@ -4134,13 +4034,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>19330051920420</v>
+        <v>19330051920286</v>
       </c>
       <c r="B18" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="D18" t="s">
         <v>139</v>
@@ -4151,13 +4051,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>19330051920447</v>
+        <v>18330051920336</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>140</v>
@@ -4168,13 +4068,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>19330051920286</v>
+        <v>19330051920287</v>
       </c>
       <c r="B20" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>141</v>
@@ -4185,13 +4085,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>18330051920336</v>
+        <v>19330051920289</v>
       </c>
       <c r="B21" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="D21" t="s">
         <v>142</v>
@@ -4202,13 +4102,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>19330051920287</v>
+        <v>19330051920343</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
         <v>143</v>
@@ -4219,13 +4119,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>19330051920343</v>
+        <v>19330051920292</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D23" t="s">
         <v>144</v>
@@ -4236,13 +4136,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920292</v>
+        <v>19330051920293</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="D24" t="s">
         <v>145</v>
@@ -4253,13 +4153,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920293</v>
+        <v>19330051920294</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="D25" t="s">
         <v>146</v>
@@ -4270,13 +4170,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>19330051920294</v>
+        <v>19330051920296</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D26" t="s">
         <v>147</v>
@@ -4287,13 +4187,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>19330051920296</v>
+        <v>19330051920295</v>
       </c>
       <c r="B27" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D27" t="s">
         <v>148</v>
@@ -4304,13 +4204,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920295</v>
+        <v>19330051920297</v>
       </c>
       <c r="B28" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="D28" t="s">
         <v>149</v>
@@ -4321,16 +4221,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920297</v>
+        <v>19330051920298</v>
       </c>
       <c r="B29" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C29" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="D29" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4338,16 +4238,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>19330051920298</v>
+        <v>19330051920299</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="C30" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4355,13 +4255,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>19330051920299</v>
+        <v>19330051920301</v>
       </c>
       <c r="B31" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>151</v>
@@ -4372,13 +4272,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>19330051920301</v>
+        <v>18330051920346</v>
       </c>
       <c r="B32" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D32" t="s">
         <v>152</v>
@@ -4392,10 +4292,10 @@
         <v>19330051920443</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" t="s">
         <v>153</v>
@@ -4409,10 +4309,10 @@
         <v>19330051920300</v>
       </c>
       <c r="B34" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="C34" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D34" t="s">
         <v>154</v>
@@ -4426,10 +4326,10 @@
         <v>19330051920305</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D35" t="s">
         <v>155</v>
@@ -4445,7 +4345,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4477,19 +4377,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920273</v>
+        <v>19330051920286</v>
       </c>
       <c r="B2" t="s">
         <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -4500,16 +4400,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920273</v>
+        <v>19330051920286</v>
       </c>
       <c r="B3" t="s">
         <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -4523,39 +4423,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>19330051920284</v>
+        <v>19330051920443</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920284</v>
+        <v>19330051920443</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="C5" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>153</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -4569,45 +4469,45 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>19330051920289</v>
+        <v>19330051920269</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920289</v>
+        <v>19330051920273</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4615,22 +4515,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>18330051920346</v>
+        <v>18330051920242</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="D8" t="s">
-        <v>76</v>
+        <v>130</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -4638,39 +4538,39 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>18330051920346</v>
+        <v>18330051920319</v>
       </c>
       <c r="B9" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920269</v>
+        <v>18330051920321</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -4684,22 +4584,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920268</v>
+        <v>19330051920278</v>
       </c>
       <c r="B11" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4707,16 +4607,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>18330051920242</v>
+        <v>19330051920284</v>
       </c>
       <c r="B12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -4730,22 +4630,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>18330051920319</v>
+        <v>19330051920289</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C13" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4753,16 +4653,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>18330051920321</v>
+        <v>19330051920292</v>
       </c>
       <c r="B14" t="s">
         <v>85</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -4776,16 +4676,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920278</v>
+        <v>19330051920293</v>
       </c>
       <c r="B15" t="s">
         <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -4799,16 +4699,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>19330051920449</v>
+        <v>19330051920299</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -4822,208 +4722,24 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>18330051920336</v>
+        <v>19330051920301</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>19330051920343</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" t="s">
-        <v>144</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>19330051920292</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" t="s">
-        <v>145</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>19330051920293</v>
-      </c>
-      <c r="B20" t="s">
-        <v>95</v>
-      </c>
-      <c r="C20" t="s">
-        <v>119</v>
-      </c>
-      <c r="D20" t="s">
-        <v>146</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>19330051920295</v>
-      </c>
-      <c r="B21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C21" t="s">
-        <v>121</v>
-      </c>
-      <c r="D21" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>19330051920298</v>
-      </c>
-      <c r="B22" t="s">
-        <v>99</v>
-      </c>
-      <c r="C22" t="s">
-        <v>122</v>
-      </c>
-      <c r="D22" t="s">
-        <v>148</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>19330051920299</v>
-      </c>
-      <c r="B23" t="s">
-        <v>100</v>
-      </c>
-      <c r="C23" t="s">
-        <v>123</v>
-      </c>
-      <c r="D23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>19330051920301</v>
-      </c>
-      <c r="B24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" t="s">
-        <v>124</v>
-      </c>
-      <c r="D24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>55</v>
-      </c>
-      <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>19330051920443</v>
-      </c>
-      <c r="B25" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" t="s">
-        <v>125</v>
-      </c>
-      <c r="D25" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>55</v>
-      </c>
-      <c r="G25">
         <v>5</v>
       </c>
     </row>
